--- a/public/samples/bb-templates/BB-Template-Import-cp-vii.xlsx
+++ b/public/samples/bb-templates/BB-Template-Import-cp-vii.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,6 +444,9 @@
       <c r="M1" t="str">
         <v>detect_keys</v>
       </c>
+      <c r="N1" t="str">
+        <v>auto_discover_tabs</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -456,7 +459,7 @@
         <v>B</v>
       </c>
       <c r="D2" t="str">
-        <v>BB</v>
+        <v>BB - Onshore</v>
       </c>
       <c r="E2">
         <v>84</v>
@@ -468,7 +471,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -485,17 +488,20 @@
       <c r="M2" t="str">
         <v/>
       </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -528,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>BB</v>
+        <v>BB - Onshore</v>
       </c>
       <c r="D2">
         <v>84</v>
@@ -543,9 +549,32 @@
         <v>["Investor","Total Capital Commitments","% of Eligible Commitments","% of All Commitments","Contributions Called to Date","Unfunded Commitment","Excess Concentration %","Excess Concentration","Eligible Contribution","Advance Rate","Availability"]</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>LP_GRID</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>BB - Offshore</v>
+      </c>
+      <c r="D3">
+        <v>84</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Total,Subtotal,Sub-Total,Grand Total,Sum,Net Total</v>
+      </c>
+      <c r="G3" t="str">
+        <v>["Investor","Total Capital Commitments","% of Eligible Commitments","% of All Commitments","Contributions Called to Date","Unfunded Commitment","Excess Concentration %","Excess Concentration","Eligible Contribution","Advance Rate","Availability"]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>
